--- a/Timesheet-evaluation-Felana-ETU1710.xlsx
+++ b/Timesheet-evaluation-Felana-ETU1710.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Dossier Git\Evaluation-Saison5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30DD9D9-6176-4A3E-A7D6-9CC40BD11CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DF4A70-D51B-4C8D-B171-D6FD7AB2419E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{326CDC2B-B960-2746-B82E-7E70916B4721}"/>
   </bookViews>
@@ -926,17 +926,17 @@
         <v>15</v>
       </c>
       <c r="D18" s="3">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E18" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F18" s="4">
         <v>15</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -950,17 +950,17 @@
         <v>29</v>
       </c>
       <c r="D19" s="3">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E19" s="3">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F19" s="4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1227,19 +1227,19 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3">
         <f>SUM(D5:D36)</f>
-        <v>555</v>
+        <v>625</v>
       </c>
       <c r="E37" s="3">
         <f>SUM(E5:E36)</f>
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="F37" s="3">
         <f>SUM(F5:F36)</f>
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="G37" s="6">
         <f>(E37/(E37+F37))</f>
-        <v>0.67256637168141598</v>
+        <v>0.72131147540983609</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
